--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700134</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127700133</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127700113</v>
       </c>
       <c r="B4" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127700106</v>
+        <v>127700135</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729145</v>
+        <v>729230</v>
       </c>
       <c r="R5" t="n">
-        <v>7171544</v>
+        <v>7171379</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700135</v>
+        <v>127700106</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>98471</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729230</v>
+        <v>729145</v>
       </c>
       <c r="R6" t="n">
-        <v>7171379</v>
+        <v>7171544</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
         <v>127700112</v>
       </c>
       <c r="B7" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>127700132</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>127700119</v>
       </c>
       <c r="B10" t="n">
-        <v>80157</v>
+        <v>80159</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>127700115</v>
       </c>
       <c r="B11" t="n">
-        <v>80157</v>
+        <v>80159</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700110</v>
+        <v>127700128</v>
       </c>
       <c r="B12" t="n">
-        <v>97331</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729293</v>
+        <v>729295</v>
       </c>
       <c r="R12" t="n">
-        <v>7171401</v>
+        <v>7171242</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127700128</v>
+        <v>127700110</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>97333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729295</v>
+        <v>729293</v>
       </c>
       <c r="R13" t="n">
-        <v>7171242</v>
+        <v>7171401</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,7 +1847,7 @@
         <v>127700099</v>
       </c>
       <c r="B14" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127700136</v>
+        <v>127700121</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>78778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729246</v>
+        <v>728982</v>
       </c>
       <c r="R15" t="n">
-        <v>7171401</v>
+        <v>7171540</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127700121</v>
+        <v>127700136</v>
       </c>
       <c r="B16" t="n">
-        <v>78776</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>728982</v>
+        <v>729246</v>
       </c>
       <c r="R16" t="n">
-        <v>7171540</v>
+        <v>7171401</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127700120</v>
+        <v>127700130</v>
       </c>
       <c r="B17" t="n">
-        <v>78776</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729080</v>
+        <v>729264</v>
       </c>
       <c r="R17" t="n">
-        <v>7171539</v>
+        <v>7171268</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127700130</v>
+        <v>127700120</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>78778</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729264</v>
+        <v>729080</v>
       </c>
       <c r="R18" t="n">
-        <v>7171268</v>
+        <v>7171539</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
         <v>127700140</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>127700137</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700128</v>
+        <v>127700099</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729295</v>
+        <v>729135</v>
       </c>
       <c r="R12" t="n">
-        <v>7171242</v>
+        <v>7171539</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127700110</v>
+        <v>127700128</v>
       </c>
       <c r="B13" t="n">
-        <v>97333</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729293</v>
+        <v>729295</v>
       </c>
       <c r="R13" t="n">
-        <v>7171401</v>
+        <v>7171242</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127700099</v>
+        <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>79052</v>
+        <v>97333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729135</v>
+        <v>729293</v>
       </c>
       <c r="R14" t="n">
-        <v>7171539</v>
+        <v>7171401</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127700121</v>
+        <v>127700136</v>
       </c>
       <c r="B15" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>728982</v>
+        <v>729246</v>
       </c>
       <c r="R15" t="n">
-        <v>7171540</v>
+        <v>7171401</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127700136</v>
+        <v>127700121</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729246</v>
+        <v>728982</v>
       </c>
       <c r="R16" t="n">
-        <v>7171401</v>
+        <v>7171540</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127700130</v>
+        <v>127700120</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729264</v>
+        <v>729080</v>
       </c>
       <c r="R17" t="n">
-        <v>7171268</v>
+        <v>7171539</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127700120</v>
+        <v>127700130</v>
       </c>
       <c r="B18" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729080</v>
+        <v>729264</v>
       </c>
       <c r="R18" t="n">
-        <v>7171539</v>
+        <v>7171268</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700099</v>
+        <v>127700128</v>
       </c>
       <c r="B12" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729135</v>
+        <v>729295</v>
       </c>
       <c r="R12" t="n">
-        <v>7171539</v>
+        <v>7171242</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127700128</v>
+        <v>127700110</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>97333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729295</v>
+        <v>729293</v>
       </c>
       <c r="R13" t="n">
-        <v>7171242</v>
+        <v>7171401</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127700110</v>
+        <v>127700099</v>
       </c>
       <c r="B14" t="n">
-        <v>97333</v>
+        <v>79052</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729293</v>
+        <v>729135</v>
       </c>
       <c r="R14" t="n">
-        <v>7171401</v>
+        <v>7171539</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127700120</v>
+        <v>127700130</v>
       </c>
       <c r="B17" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729080</v>
+        <v>729264</v>
       </c>
       <c r="R17" t="n">
-        <v>7171539</v>
+        <v>7171268</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127700130</v>
+        <v>127700120</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729264</v>
+        <v>729080</v>
       </c>
       <c r="R18" t="n">
-        <v>7171268</v>
+        <v>7171539</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700128</v>
+        <v>127700110</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>97333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729295</v>
+        <v>729293</v>
       </c>
       <c r="R12" t="n">
-        <v>7171242</v>
+        <v>7171401</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127700110</v>
+        <v>127700099</v>
       </c>
       <c r="B13" t="n">
-        <v>97333</v>
+        <v>79052</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729293</v>
+        <v>729135</v>
       </c>
       <c r="R13" t="n">
-        <v>7171401</v>
+        <v>7171539</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127700099</v>
+        <v>127700128</v>
       </c>
       <c r="B14" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729135</v>
+        <v>729295</v>
       </c>
       <c r="R14" t="n">
-        <v>7171539</v>
+        <v>7171242</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127700130</v>
+        <v>127700120</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729264</v>
+        <v>729080</v>
       </c>
       <c r="R17" t="n">
-        <v>7171268</v>
+        <v>7171539</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127700120</v>
+        <v>127700130</v>
       </c>
       <c r="B18" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729080</v>
+        <v>729264</v>
       </c>
       <c r="R18" t="n">
-        <v>7171539</v>
+        <v>7171268</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -1071,7 +1071,7 @@
         <v>127700106</v>
       </c>
       <c r="B6" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700110</v>
+        <v>127700099</v>
       </c>
       <c r="B12" t="n">
-        <v>97333</v>
+        <v>79052</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729293</v>
+        <v>729135</v>
       </c>
       <c r="R12" t="n">
-        <v>7171401</v>
+        <v>7171539</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127700099</v>
+        <v>127700128</v>
       </c>
       <c r="B13" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729135</v>
+        <v>729295</v>
       </c>
       <c r="R13" t="n">
-        <v>7171539</v>
+        <v>7171242</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127700128</v>
+        <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>97339</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729295</v>
+        <v>729293</v>
       </c>
       <c r="R14" t="n">
-        <v>7171242</v>
+        <v>7171401</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127700120</v>
+        <v>127700130</v>
       </c>
       <c r="B17" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729080</v>
+        <v>729264</v>
       </c>
       <c r="R17" t="n">
-        <v>7171539</v>
+        <v>7171268</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127700130</v>
+        <v>127700120</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729264</v>
+        <v>729080</v>
       </c>
       <c r="R18" t="n">
-        <v>7171268</v>
+        <v>7171539</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700134</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127700133</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127700113</v>
       </c>
       <c r="B4" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127700135</v>
+        <v>127700106</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>98480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729230</v>
+        <v>729145</v>
       </c>
       <c r="R5" t="n">
-        <v>7171379</v>
+        <v>7171544</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700106</v>
+        <v>127700135</v>
       </c>
       <c r="B6" t="n">
-        <v>98477</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729145</v>
+        <v>729230</v>
       </c>
       <c r="R6" t="n">
-        <v>7171544</v>
+        <v>7171379</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
         <v>127700112</v>
       </c>
       <c r="B7" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>127700132</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127700142</v>
+        <v>127700119</v>
       </c>
       <c r="B9" t="n">
-        <v>92628</v>
+        <v>80162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729271</v>
+        <v>729114</v>
       </c>
       <c r="R9" t="n">
-        <v>7171408</v>
+        <v>7171530</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127700119</v>
+        <v>127700115</v>
       </c>
       <c r="B10" t="n">
-        <v>80159</v>
+        <v>80162</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729114</v>
+        <v>729246</v>
       </c>
       <c r="R10" t="n">
-        <v>7171530</v>
+        <v>7171401</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127700115</v>
+        <v>127700142</v>
       </c>
       <c r="B11" t="n">
-        <v>80159</v>
+        <v>92631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729246</v>
+        <v>729271</v>
       </c>
       <c r="R11" t="n">
-        <v>7171401</v>
+        <v>7171408</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700099</v>
+        <v>127700128</v>
       </c>
       <c r="B12" t="n">
-        <v>79052</v>
+        <v>79023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729135</v>
+        <v>729295</v>
       </c>
       <c r="R12" t="n">
-        <v>7171539</v>
+        <v>7171242</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127700128</v>
+        <v>127700099</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79055</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729295</v>
+        <v>729135</v>
       </c>
       <c r="R13" t="n">
-        <v>7171242</v>
+        <v>7171539</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,7 +1847,7 @@
         <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>127700136</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>127700121</v>
       </c>
       <c r="B16" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>127700130</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>127700120</v>
       </c>
       <c r="B18" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>127700140</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>127700137</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700134</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127700133</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127700113</v>
       </c>
       <c r="B4" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127700106</v>
       </c>
       <c r="B5" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127700135</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>127700112</v>
       </c>
       <c r="B7" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>127700132</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127700119</v>
+        <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>80162</v>
+        <v>92639</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729114</v>
+        <v>729271</v>
       </c>
       <c r="R9" t="n">
-        <v>7171530</v>
+        <v>7171408</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127700115</v>
+        <v>127700119</v>
       </c>
       <c r="B10" t="n">
-        <v>80162</v>
+        <v>80168</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729246</v>
+        <v>729114</v>
       </c>
       <c r="R10" t="n">
-        <v>7171401</v>
+        <v>7171530</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127700142</v>
+        <v>127700115</v>
       </c>
       <c r="B11" t="n">
-        <v>92631</v>
+        <v>80168</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729271</v>
+        <v>729246</v>
       </c>
       <c r="R11" t="n">
-        <v>7171408</v>
+        <v>7171401</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700128</v>
+        <v>127700099</v>
       </c>
       <c r="B12" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729295</v>
+        <v>729135</v>
       </c>
       <c r="R12" t="n">
-        <v>7171242</v>
+        <v>7171539</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127700099</v>
+        <v>127700128</v>
       </c>
       <c r="B13" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729135</v>
+        <v>729295</v>
       </c>
       <c r="R13" t="n">
-        <v>7171539</v>
+        <v>7171242</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,7 +1847,7 @@
         <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127700136</v>
+        <v>127700121</v>
       </c>
       <c r="B15" t="n">
-        <v>79023</v>
+        <v>78787</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729246</v>
+        <v>728982</v>
       </c>
       <c r="R15" t="n">
-        <v>7171401</v>
+        <v>7171540</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127700121</v>
+        <v>127700136</v>
       </c>
       <c r="B16" t="n">
-        <v>78781</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>728982</v>
+        <v>729246</v>
       </c>
       <c r="R16" t="n">
-        <v>7171540</v>
+        <v>7171401</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127700130</v>
+        <v>127700120</v>
       </c>
       <c r="B17" t="n">
-        <v>79023</v>
+        <v>78787</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729264</v>
+        <v>729080</v>
       </c>
       <c r="R17" t="n">
-        <v>7171268</v>
+        <v>7171539</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127700120</v>
+        <v>127700130</v>
       </c>
       <c r="B18" t="n">
-        <v>78781</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729080</v>
+        <v>729264</v>
       </c>
       <c r="R18" t="n">
-        <v>7171539</v>
+        <v>7171268</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
         <v>127700140</v>
       </c>
       <c r="B19" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>127700137</v>
       </c>
       <c r="B20" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127700106</v>
+        <v>127700135</v>
       </c>
       <c r="B5" t="n">
-        <v>98488</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729145</v>
+        <v>729230</v>
       </c>
       <c r="R5" t="n">
-        <v>7171544</v>
+        <v>7171379</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700135</v>
+        <v>127700106</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>98489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729230</v>
+        <v>729145</v>
       </c>
       <c r="R6" t="n">
-        <v>7171379</v>
+        <v>7171544</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127700142</v>
+        <v>127700119</v>
       </c>
       <c r="B9" t="n">
-        <v>92639</v>
+        <v>80168</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729271</v>
+        <v>729114</v>
       </c>
       <c r="R9" t="n">
-        <v>7171408</v>
+        <v>7171530</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127700119</v>
+        <v>127700115</v>
       </c>
       <c r="B10" t="n">
         <v>80168</v>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729114</v>
+        <v>729246</v>
       </c>
       <c r="R10" t="n">
-        <v>7171530</v>
+        <v>7171401</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127700115</v>
+        <v>127700142</v>
       </c>
       <c r="B11" t="n">
-        <v>80168</v>
+        <v>92640</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729246</v>
+        <v>729271</v>
       </c>
       <c r="R11" t="n">
-        <v>7171401</v>
+        <v>7171408</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700099</v>
+        <v>127700128</v>
       </c>
       <c r="B12" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729135</v>
+        <v>729295</v>
       </c>
       <c r="R12" t="n">
-        <v>7171539</v>
+        <v>7171242</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127700128</v>
+        <v>127700110</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>97351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729295</v>
+        <v>729293</v>
       </c>
       <c r="R13" t="n">
-        <v>7171242</v>
+        <v>7171401</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127700110</v>
+        <v>127700099</v>
       </c>
       <c r="B14" t="n">
-        <v>97350</v>
+        <v>79061</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729293</v>
+        <v>729135</v>
       </c>
       <c r="R14" t="n">
-        <v>7171401</v>
+        <v>7171539</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127700121</v>
+        <v>127700136</v>
       </c>
       <c r="B15" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>728982</v>
+        <v>729246</v>
       </c>
       <c r="R15" t="n">
-        <v>7171540</v>
+        <v>7171401</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127700136</v>
+        <v>127700121</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729246</v>
+        <v>728982</v>
       </c>
       <c r="R16" t="n">
-        <v>7171401</v>
+        <v>7171540</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127700120</v>
+        <v>127700130</v>
       </c>
       <c r="B17" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729080</v>
+        <v>729264</v>
       </c>
       <c r="R17" t="n">
-        <v>7171539</v>
+        <v>7171268</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127700130</v>
+        <v>127700120</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729264</v>
+        <v>729080</v>
       </c>
       <c r="R18" t="n">
-        <v>7171268</v>
+        <v>7171539</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127700119</v>
+        <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>80168</v>
+        <v>92640</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729114</v>
+        <v>729271</v>
       </c>
       <c r="R9" t="n">
-        <v>7171530</v>
+        <v>7171408</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127700115</v>
+        <v>127700119</v>
       </c>
       <c r="B10" t="n">
         <v>80168</v>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729246</v>
+        <v>729114</v>
       </c>
       <c r="R10" t="n">
-        <v>7171401</v>
+        <v>7171530</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127700142</v>
+        <v>127700115</v>
       </c>
       <c r="B11" t="n">
-        <v>92640</v>
+        <v>80168</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729271</v>
+        <v>729246</v>
       </c>
       <c r="R11" t="n">
-        <v>7171408</v>
+        <v>7171401</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127700110</v>
+        <v>127700099</v>
       </c>
       <c r="B13" t="n">
-        <v>97351</v>
+        <v>79061</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729293</v>
+        <v>729135</v>
       </c>
       <c r="R13" t="n">
-        <v>7171401</v>
+        <v>7171539</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127700099</v>
+        <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>79061</v>
+        <v>97351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729135</v>
+        <v>729293</v>
       </c>
       <c r="R14" t="n">
-        <v>7171539</v>
+        <v>7171401</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127700136</v>
+        <v>127700121</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729246</v>
+        <v>728982</v>
       </c>
       <c r="R15" t="n">
-        <v>7171401</v>
+        <v>7171540</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127700121</v>
+        <v>127700136</v>
       </c>
       <c r="B16" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>728982</v>
+        <v>729246</v>
       </c>
       <c r="R16" t="n">
-        <v>7171540</v>
+        <v>7171401</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127700130</v>
+        <v>127700120</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729264</v>
+        <v>729080</v>
       </c>
       <c r="R17" t="n">
-        <v>7171268</v>
+        <v>7171539</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127700120</v>
+        <v>127700130</v>
       </c>
       <c r="B18" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729080</v>
+        <v>729264</v>
       </c>
       <c r="R18" t="n">
-        <v>7171539</v>
+        <v>7171268</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -1071,7 +1071,7 @@
         <v>127700106</v>
       </c>
       <c r="B6" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700128</v>
+        <v>127700110</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>97352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729295</v>
+        <v>729293</v>
       </c>
       <c r="R12" t="n">
-        <v>7171242</v>
+        <v>7171401</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127700110</v>
+        <v>127700128</v>
       </c>
       <c r="B14" t="n">
-        <v>97351</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729293</v>
+        <v>729295</v>
       </c>
       <c r="R14" t="n">
-        <v>7171401</v>
+        <v>7171242</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127700121</v>
+        <v>127700136</v>
       </c>
       <c r="B15" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>728982</v>
+        <v>729246</v>
       </c>
       <c r="R15" t="n">
-        <v>7171540</v>
+        <v>7171401</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127700136</v>
+        <v>127700121</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729246</v>
+        <v>728982</v>
       </c>
       <c r="R16" t="n">
-        <v>7171401</v>
+        <v>7171540</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -1071,7 +1071,7 @@
         <v>127700106</v>
       </c>
       <c r="B6" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127700142</v>
+        <v>127700119</v>
       </c>
       <c r="B9" t="n">
-        <v>92641</v>
+        <v>80168</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729271</v>
+        <v>729114</v>
       </c>
       <c r="R9" t="n">
-        <v>7171408</v>
+        <v>7171530</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127700119</v>
+        <v>127700115</v>
       </c>
       <c r="B10" t="n">
         <v>80168</v>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729114</v>
+        <v>729246</v>
       </c>
       <c r="R10" t="n">
-        <v>7171530</v>
+        <v>7171401</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127700115</v>
+        <v>127700142</v>
       </c>
       <c r="B11" t="n">
-        <v>80168</v>
+        <v>92642</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729246</v>
+        <v>729271</v>
       </c>
       <c r="R11" t="n">
-        <v>7171401</v>
+        <v>7171408</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700110</v>
+        <v>127700099</v>
       </c>
       <c r="B12" t="n">
-        <v>97352</v>
+        <v>79061</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729293</v>
+        <v>729135</v>
       </c>
       <c r="R12" t="n">
-        <v>7171401</v>
+        <v>7171539</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127700099</v>
+        <v>127700128</v>
       </c>
       <c r="B13" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729135</v>
+        <v>729295</v>
       </c>
       <c r="R13" t="n">
-        <v>7171539</v>
+        <v>7171242</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127700128</v>
+        <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>97353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729295</v>
+        <v>729293</v>
       </c>
       <c r="R14" t="n">
-        <v>7171242</v>
+        <v>7171401</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127700135</v>
+        <v>127700106</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>98491</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729230</v>
+        <v>729145</v>
       </c>
       <c r="R5" t="n">
-        <v>7171379</v>
+        <v>7171544</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700106</v>
+        <v>127700135</v>
       </c>
       <c r="B6" t="n">
-        <v>98491</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729145</v>
+        <v>729230</v>
       </c>
       <c r="R6" t="n">
-        <v>7171544</v>
+        <v>7171379</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127700119</v>
+        <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>80168</v>
+        <v>92642</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729114</v>
+        <v>729271</v>
       </c>
       <c r="R9" t="n">
-        <v>7171530</v>
+        <v>7171408</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127700115</v>
+        <v>127700119</v>
       </c>
       <c r="B10" t="n">
         <v>80168</v>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729246</v>
+        <v>729114</v>
       </c>
       <c r="R10" t="n">
-        <v>7171401</v>
+        <v>7171530</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127700142</v>
+        <v>127700115</v>
       </c>
       <c r="B11" t="n">
-        <v>92642</v>
+        <v>80168</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>729271</v>
+        <v>729246</v>
       </c>
       <c r="R11" t="n">
-        <v>7171408</v>
+        <v>7171401</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700099</v>
+        <v>127700128</v>
       </c>
       <c r="B12" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729135</v>
+        <v>729295</v>
       </c>
       <c r="R12" t="n">
-        <v>7171539</v>
+        <v>7171242</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127700128</v>
+        <v>127700099</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729295</v>
+        <v>729135</v>
       </c>
       <c r="R13" t="n">
-        <v>7171242</v>
+        <v>7171539</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127700136</v>
+        <v>127700121</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729246</v>
+        <v>728982</v>
       </c>
       <c r="R15" t="n">
-        <v>7171401</v>
+        <v>7171540</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127700121</v>
+        <v>127700136</v>
       </c>
       <c r="B16" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>728982</v>
+        <v>729246</v>
       </c>
       <c r="R16" t="n">
-        <v>7171540</v>
+        <v>7171401</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127700106</v>
+        <v>127700135</v>
       </c>
       <c r="B5" t="n">
-        <v>98491</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729145</v>
+        <v>729230</v>
       </c>
       <c r="R5" t="n">
-        <v>7171544</v>
+        <v>7171379</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700135</v>
+        <v>127700106</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>98491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729230</v>
+        <v>729145</v>
       </c>
       <c r="R6" t="n">
-        <v>7171379</v>
+        <v>7171544</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700128</v>
+        <v>127700099</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729295</v>
+        <v>729135</v>
       </c>
       <c r="R12" t="n">
-        <v>7171242</v>
+        <v>7171539</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127700099</v>
+        <v>127700128</v>
       </c>
       <c r="B13" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729135</v>
+        <v>729295</v>
       </c>
       <c r="R13" t="n">
-        <v>7171539</v>
+        <v>7171242</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700099</v>
+        <v>127700128</v>
       </c>
       <c r="B12" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729135</v>
+        <v>729295</v>
       </c>
       <c r="R12" t="n">
-        <v>7171539</v>
+        <v>7171242</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127700128</v>
+        <v>127700099</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729295</v>
+        <v>729135</v>
       </c>
       <c r="R13" t="n">
-        <v>7171242</v>
+        <v>7171539</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127700121</v>
+        <v>127700136</v>
       </c>
       <c r="B15" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>728982</v>
+        <v>729246</v>
       </c>
       <c r="R15" t="n">
-        <v>7171540</v>
+        <v>7171401</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127700136</v>
+        <v>127700121</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729246</v>
+        <v>728982</v>
       </c>
       <c r="R16" t="n">
-        <v>7171401</v>
+        <v>7171540</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127700120</v>
+        <v>127700130</v>
       </c>
       <c r="B17" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729080</v>
+        <v>729264</v>
       </c>
       <c r="R17" t="n">
-        <v>7171539</v>
+        <v>7171268</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127700130</v>
+        <v>127700120</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729264</v>
+        <v>729080</v>
       </c>
       <c r="R18" t="n">
-        <v>7171268</v>
+        <v>7171539</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127700135</v>
+        <v>127700106</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>98491</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729230</v>
+        <v>729145</v>
       </c>
       <c r="R5" t="n">
-        <v>7171379</v>
+        <v>7171544</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700106</v>
+        <v>127700135</v>
       </c>
       <c r="B6" t="n">
-        <v>98491</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729145</v>
+        <v>729230</v>
       </c>
       <c r="R6" t="n">
-        <v>7171544</v>
+        <v>7171379</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700128</v>
+        <v>127700099</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729295</v>
+        <v>729135</v>
       </c>
       <c r="R12" t="n">
-        <v>7171242</v>
+        <v>7171539</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127700099</v>
+        <v>127700128</v>
       </c>
       <c r="B13" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729135</v>
+        <v>729295</v>
       </c>
       <c r="R13" t="n">
-        <v>7171539</v>
+        <v>7171242</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127700136</v>
+        <v>127700121</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729246</v>
+        <v>728982</v>
       </c>
       <c r="R15" t="n">
-        <v>7171401</v>
+        <v>7171540</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127700121</v>
+        <v>127700136</v>
       </c>
       <c r="B16" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>728982</v>
+        <v>729246</v>
       </c>
       <c r="R16" t="n">
-        <v>7171540</v>
+        <v>7171401</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127700130</v>
+        <v>127700120</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729264</v>
+        <v>729080</v>
       </c>
       <c r="R17" t="n">
-        <v>7171268</v>
+        <v>7171539</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127700120</v>
+        <v>127700130</v>
       </c>
       <c r="B18" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729080</v>
+        <v>729264</v>
       </c>
       <c r="R18" t="n">
-        <v>7171539</v>
+        <v>7171268</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127700106</v>
+        <v>127700135</v>
       </c>
       <c r="B5" t="n">
-        <v>98491</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729145</v>
+        <v>729230</v>
       </c>
       <c r="R5" t="n">
-        <v>7171544</v>
+        <v>7171379</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700135</v>
+        <v>127700106</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>98491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729230</v>
+        <v>729145</v>
       </c>
       <c r="R6" t="n">
-        <v>7171379</v>
+        <v>7171544</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127700121</v>
+        <v>127700136</v>
       </c>
       <c r="B15" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>728982</v>
+        <v>729246</v>
       </c>
       <c r="R15" t="n">
-        <v>7171540</v>
+        <v>7171401</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127700136</v>
+        <v>127700121</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729246</v>
+        <v>728982</v>
       </c>
       <c r="R16" t="n">
-        <v>7171401</v>
+        <v>7171540</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700134</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127700133</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127700113</v>
       </c>
       <c r="B4" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127700135</v>
+        <v>127700106</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>98499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>729230</v>
+        <v>729145</v>
       </c>
       <c r="R5" t="n">
-        <v>7171379</v>
+        <v>7171544</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127700106</v>
+        <v>127700135</v>
       </c>
       <c r="B6" t="n">
-        <v>98491</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>729145</v>
+        <v>729230</v>
       </c>
       <c r="R6" t="n">
-        <v>7171544</v>
+        <v>7171379</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
         <v>127700112</v>
       </c>
       <c r="B7" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>127700132</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>127700119</v>
       </c>
       <c r="B10" t="n">
-        <v>80168</v>
+        <v>80171</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>127700115</v>
       </c>
       <c r="B11" t="n">
-        <v>80168</v>
+        <v>80171</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700099</v>
+        <v>127700128</v>
       </c>
       <c r="B12" t="n">
-        <v>79061</v>
+        <v>79032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729135</v>
+        <v>729295</v>
       </c>
       <c r="R12" t="n">
-        <v>7171539</v>
+        <v>7171242</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127700128</v>
+        <v>127700110</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>97361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729295</v>
+        <v>729293</v>
       </c>
       <c r="R13" t="n">
-        <v>7171242</v>
+        <v>7171401</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127700110</v>
+        <v>127700099</v>
       </c>
       <c r="B14" t="n">
-        <v>97353</v>
+        <v>79064</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729293</v>
+        <v>729135</v>
       </c>
       <c r="R14" t="n">
-        <v>7171401</v>
+        <v>7171539</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127700136</v>
+        <v>127700121</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>78790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>729246</v>
+        <v>728982</v>
       </c>
       <c r="R15" t="n">
-        <v>7171401</v>
+        <v>7171540</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127700121</v>
+        <v>127700136</v>
       </c>
       <c r="B16" t="n">
-        <v>78787</v>
+        <v>79032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>728982</v>
+        <v>729246</v>
       </c>
       <c r="R16" t="n">
-        <v>7171540</v>
+        <v>7171401</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2138,7 +2138,7 @@
         <v>127700120</v>
       </c>
       <c r="B17" t="n">
-        <v>78787</v>
+        <v>78790</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>127700130</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>127700140</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>127700137</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127700142</v>
+        <v>127700119</v>
       </c>
       <c r="B9" t="n">
-        <v>92650</v>
+        <v>80171</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729271</v>
+        <v>729114</v>
       </c>
       <c r="R9" t="n">
-        <v>7171408</v>
+        <v>7171530</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127700119</v>
+        <v>127700142</v>
       </c>
       <c r="B10" t="n">
-        <v>80171</v>
+        <v>92650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729114</v>
+        <v>729271</v>
       </c>
       <c r="R10" t="n">
-        <v>7171530</v>
+        <v>7171408</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700134</v>
       </c>
       <c r="B2" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127700133</v>
       </c>
       <c r="B3" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127700113</v>
       </c>
       <c r="B4" t="n">
-        <v>80135</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127700106</v>
       </c>
       <c r="B5" t="n">
-        <v>98499</v>
+        <v>98511</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127700135</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>127700112</v>
       </c>
       <c r="B7" t="n">
-        <v>80135</v>
+        <v>80146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>127700132</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127700119</v>
+        <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>80171</v>
+        <v>92661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>729114</v>
+        <v>729271</v>
       </c>
       <c r="R9" t="n">
-        <v>7171530</v>
+        <v>7171408</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127700142</v>
+        <v>127700119</v>
       </c>
       <c r="B10" t="n">
-        <v>92650</v>
+        <v>80182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>729271</v>
+        <v>729114</v>
       </c>
       <c r="R10" t="n">
-        <v>7171408</v>
+        <v>7171530</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
         <v>127700115</v>
       </c>
       <c r="B11" t="n">
-        <v>80171</v>
+        <v>80182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127700128</v>
+        <v>127700099</v>
       </c>
       <c r="B12" t="n">
-        <v>79032</v>
+        <v>79075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>729295</v>
+        <v>729135</v>
       </c>
       <c r="R12" t="n">
-        <v>7171242</v>
+        <v>7171539</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127700110</v>
+        <v>127700128</v>
       </c>
       <c r="B13" t="n">
-        <v>97361</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>729293</v>
+        <v>729295</v>
       </c>
       <c r="R13" t="n">
-        <v>7171401</v>
+        <v>7171242</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127700099</v>
+        <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>79064</v>
+        <v>97373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>729135</v>
+        <v>729293</v>
       </c>
       <c r="R14" t="n">
-        <v>7171539</v>
+        <v>7171401</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127700121</v>
+        <v>127700136</v>
       </c>
       <c r="B15" t="n">
-        <v>78790</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>728982</v>
+        <v>729246</v>
       </c>
       <c r="R15" t="n">
-        <v>7171540</v>
+        <v>7171401</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127700136</v>
+        <v>127700121</v>
       </c>
       <c r="B16" t="n">
-        <v>79032</v>
+        <v>78801</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>729246</v>
+        <v>728982</v>
       </c>
       <c r="R16" t="n">
-        <v>7171401</v>
+        <v>7171540</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127700120</v>
+        <v>127700130</v>
       </c>
       <c r="B17" t="n">
-        <v>78790</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>729080</v>
+        <v>729264</v>
       </c>
       <c r="R17" t="n">
-        <v>7171539</v>
+        <v>7171268</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127700130</v>
+        <v>127700120</v>
       </c>
       <c r="B18" t="n">
-        <v>79032</v>
+        <v>78801</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2243,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>729264</v>
+        <v>729080</v>
       </c>
       <c r="R18" t="n">
-        <v>7171268</v>
+        <v>7171539</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2332,7 +2332,7 @@
         <v>127700140</v>
       </c>
       <c r="B19" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>127700137</v>
       </c>
       <c r="B20" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700134</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>127700133</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -870,14 +874,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>127700113</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>80225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,14 +975,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>127700106</v>
       </c>
       <c r="B5" t="n">
-        <v>98511</v>
+        <v>98653</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1064,14 +1076,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>127700135</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,14 +1177,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>127700112</v>
       </c>
       <c r="B7" t="n">
-        <v>80146</v>
+        <v>80225</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,14 +1278,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>127700132</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,14 +1379,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>92661</v>
+        <v>92794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,14 +1480,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>127700119</v>
       </c>
       <c r="B10" t="n">
-        <v>80182</v>
+        <v>80261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1549,14 +1581,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>127700115</v>
       </c>
       <c r="B11" t="n">
-        <v>80182</v>
+        <v>80261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1646,14 +1682,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>127700099</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>79152</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1743,14 +1783,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>127700128</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1840,14 +1884,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>97373</v>
+        <v>97509</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1937,14 +1985,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>127700136</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2034,14 +2086,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>127700121</v>
       </c>
       <c r="B16" t="n">
-        <v>78801</v>
+        <v>78877</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2131,14 +2187,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>127700130</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2228,14 +2288,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>127700120</v>
       </c>
       <c r="B18" t="n">
-        <v>78801</v>
+        <v>78877</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2325,14 +2389,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>127700140</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2422,14 +2490,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>127700137</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2519,7 +2591,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700134</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127700133</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127700113</v>
       </c>
       <c r="B4" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>127700106</v>
       </c>
       <c r="B5" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>127700135</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127700112</v>
       </c>
       <c r="B7" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127700132</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127700119</v>
       </c>
       <c r="B10" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>127700115</v>
       </c>
       <c r="B11" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127700099</v>
       </c>
       <c r="B12" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>127700128</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>97509</v>
+        <v>97513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>127700136</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>127700121</v>
       </c>
       <c r="B16" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>127700130</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>127700120</v>
       </c>
       <c r="B18" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>127700140</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>127700137</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700134</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127700133</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127700113</v>
       </c>
       <c r="B4" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>127700106</v>
       </c>
       <c r="B5" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>127700135</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127700112</v>
       </c>
       <c r="B7" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127700132</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127700119</v>
       </c>
       <c r="B10" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>127700115</v>
       </c>
       <c r="B11" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127700099</v>
       </c>
       <c r="B12" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>127700128</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>97513</v>
+        <v>97520</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>127700136</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>127700121</v>
       </c>
       <c r="B16" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>127700130</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>127700120</v>
       </c>
       <c r="B18" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>127700140</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>127700137</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -986,7 +986,7 @@
         <v>127700106</v>
       </c>
       <c r="B5" t="n">
-        <v>98672</v>
+        <v>98677</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700134</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127700133</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127700113</v>
       </c>
       <c r="B4" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>127700106</v>
       </c>
       <c r="B5" t="n">
-        <v>98677</v>
+        <v>98680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>127700135</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127700112</v>
       </c>
       <c r="B7" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127700132</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127700119</v>
       </c>
       <c r="B10" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>127700115</v>
       </c>
       <c r="B11" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127700099</v>
       </c>
       <c r="B12" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>127700128</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>97533</v>
+        <v>97536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>127700136</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>127700121</v>
       </c>
       <c r="B16" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>127700130</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>127700120</v>
       </c>
       <c r="B18" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>127700140</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>127700137</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700134</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127700133</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127700113</v>
       </c>
       <c r="B4" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>127700106</v>
       </c>
       <c r="B5" t="n">
-        <v>98680</v>
+        <v>98690</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>127700135</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127700112</v>
       </c>
       <c r="B7" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127700132</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127700119</v>
       </c>
       <c r="B10" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>127700115</v>
       </c>
       <c r="B11" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127700099</v>
       </c>
       <c r="B12" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>127700128</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>127700136</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>127700121</v>
       </c>
       <c r="B16" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>127700130</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>127700120</v>
       </c>
       <c r="B18" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>127700140</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>127700137</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -986,7 +986,7 @@
         <v>127700106</v>
       </c>
       <c r="B5" t="n">
-        <v>98690</v>
+        <v>98697</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700134</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127700133</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127700113</v>
       </c>
       <c r="B4" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>127700106</v>
       </c>
       <c r="B5" t="n">
-        <v>98697</v>
+        <v>98699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>127700135</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127700112</v>
       </c>
       <c r="B7" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127700132</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127700119</v>
       </c>
       <c r="B10" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>127700115</v>
       </c>
       <c r="B11" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127700099</v>
       </c>
       <c r="B12" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>127700128</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>127700136</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>127700121</v>
       </c>
       <c r="B16" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>127700130</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>127700120</v>
       </c>
       <c r="B18" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>127700140</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>127700137</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -986,7 +986,7 @@
         <v>127700106</v>
       </c>
       <c r="B5" t="n">
-        <v>98699</v>
+        <v>98725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>97555</v>
+        <v>97581</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -986,7 +986,7 @@
         <v>127700106</v>
       </c>
       <c r="B5" t="n">
-        <v>98725</v>
+        <v>98726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -986,7 +986,7 @@
         <v>127700106</v>
       </c>
       <c r="B5" t="n">
-        <v>98726</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700134</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127700133</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127700113</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>127700106</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>98731</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>127700135</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127700112</v>
       </c>
       <c r="B7" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127700132</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127700119</v>
       </c>
       <c r="B10" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>127700115</v>
       </c>
       <c r="B11" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127700099</v>
       </c>
       <c r="B12" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>127700128</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>127700136</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>127700121</v>
       </c>
       <c r="B16" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>127700130</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>127700120</v>
       </c>
       <c r="B18" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>127700140</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>127700137</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127700134</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127700133</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127700113</v>
       </c>
       <c r="B4" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>127700106</v>
       </c>
       <c r="B5" t="n">
-        <v>98731</v>
+        <v>98733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>127700135</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127700112</v>
       </c>
       <c r="B7" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>127700132</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>127700119</v>
       </c>
       <c r="B10" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>127700115</v>
       </c>
       <c r="B11" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>127700099</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>127700128</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>127700136</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>127700121</v>
       </c>
       <c r="B16" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>127700130</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>127700120</v>
       </c>
       <c r="B18" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>127700140</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>127700137</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12017-2023 artfynd.xlsx
+++ b/artfynd/A 12017-2023 artfynd.xlsx
@@ -986,7 +986,7 @@
         <v>127700106</v>
       </c>
       <c r="B5" t="n">
-        <v>98733</v>
+        <v>98737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>127700142</v>
       </c>
       <c r="B9" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>127700110</v>
       </c>
       <c r="B14" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
